--- a/knowledge/episodes/2026-10/ym-sverka-postupleniya/ym-sverka-dbs-fbs-20261020.xlsx
+++ b/knowledge/episodes/2026-10/ym-sverka-postupleniya/ym-sverka-dbs-fbs-20261020.xlsx
@@ -476,14 +476,14 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Лист «ДБС»: разница 1С − Маркет. Зеркала: Маркет 2 278 235, 1С 2 712 830, разница 434 595. Мебель: Маркет 17 879 570, 1С 17 003 479, разница -876 091.</t>
+          <t>Лист «ДБС»: разница 1С − Маркет. Зеркала: Маркет 2 278 235, 1С 2 221 720, разница -56 515. Мебель: Маркет 17 879 570, 1С 17 494 589, разница -384 981.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Разница расписана: магазин ДБС без документа за месяц (минус), отклонения документов с парой (переходящие заказы), документ 1С, который лёг на ФБС-магазин (мебель май № 36 на 767 018 ₽ - ближайший к FBS OOO 825 415, при этом за май есть и реализации ФБС 709 509 ₽; зеркала август № 74 на 491 110 ₽ - равен магазину 149154933 по отчёту о реализации Маркета, при этом за август есть и реализации ФБС 489 056 ₽; в обоих случаях один магазин за месяц проведён двумя документами - проверить), документ без пары (июнь, № 43 на 401 995 ₽). Остаток 0.</t>
+          <t xml:space="preserve">   Разница расписана: магазин ДБС без документа за месяц (минус), отклонения документов с парой (переходящие заказы), документ 1С, который лёг на ФБС-магазин (мебель май № 36 на 767 018 ₽ - ближайший к FBS OOO 825 415, по отчёту Маркета о реализации FBS OOO за май 768 358; при этом за май есть и реализации ФБС 709 509 ₽ - один магазин за месяц проведён двумя документами, проверить), документ без пары (июнь, № 43 на 401 995 ₽). Остаток 0.</t>
         </is>
       </c>
     </row>
@@ -770,7 +770,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G9" s="3" t="n">
         <v>2077725</v>
@@ -836,7 +836,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G11" s="3" t="n">
         <v>1971045</v>
@@ -1317,10 +1317,10 @@
         <v>897518.02</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>1403831</v>
+        <v>912721</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>506312.98</v>
+        <v>15202.98</v>
       </c>
       <c r="F11" s="3" t="n">
         <v>0</v>
@@ -1329,7 +1329,7 @@
         <v>15202.98</v>
       </c>
       <c r="H11" s="3" t="n">
-        <v>491110</v>
+        <v>0</v>
       </c>
       <c r="I11" s="3" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>2278235.02</v>
       </c>
       <c r="D13" s="6" t="n">
-        <v>2712830</v>
+        <v>2221720</v>
       </c>
       <c r="E13" s="7" t="n">
-        <v>434594.98</v>
+        <v>-56515.02</v>
       </c>
       <c r="F13" s="6" t="n">
         <v>-56515</v>
@@ -1403,7 +1403,7 @@
         <v>-0.02</v>
       </c>
       <c r="H13" s="6" t="n">
-        <v>491110</v>
+        <v>0</v>
       </c>
       <c r="I13" s="6" t="n">
         <v>0</v>
@@ -1695,16 +1695,16 @@
         <v>1868033</v>
       </c>
       <c r="D21" s="3" t="n">
-        <v>1339229</v>
+        <v>1830339</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>-528804</v>
+        <v>-37694</v>
       </c>
       <c r="F21" s="3" t="n">
-        <v>-528804</v>
+        <v>0</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>0</v>
+        <v>-37694</v>
       </c>
       <c r="H21" s="3" t="n">
         <v>0</v>
@@ -1715,11 +1715,7 @@
       <c r="J21" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>DBS OOO 15 дней 528 804</t>
-        </is>
-      </c>
+      <c r="K21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1773,16 +1769,16 @@
         <v>17879570</v>
       </c>
       <c r="D23" s="6" t="n">
-        <v>17003479</v>
+        <v>17494589</v>
       </c>
       <c r="E23" s="7" t="n">
-        <v>-876091</v>
+        <v>-384981</v>
       </c>
       <c r="F23" s="6" t="n">
-        <v>-1697817</v>
+        <v>-1169013</v>
       </c>
       <c r="G23" s="6" t="n">
-        <v>54708</v>
+        <v>17014</v>
       </c>
       <c r="H23" s="6" t="n">
         <v>767018</v>
@@ -3509,7 +3505,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>ближайший по сумме</t>
+          <t>равен отчёту Маркета о реализации (доставлено − возвраты)</t>
         </is>
       </c>
     </row>
@@ -3607,24 +3603,28 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>149154933</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr"/>
+          <t>149002232</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>DBS OOO 15 дней</t>
+        </is>
+      </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>ФБС</t>
+          <t>ДБС</t>
         </is>
       </c>
       <c r="G27" s="3" t="n">
-        <v>479643</v>
+        <v>528804</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>11467</v>
+        <v>-37694</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>ближайший по сумме</t>
+          <t>равен отчёту Маркета о реализации (доставлено − возвраты)</t>
         </is>
       </c>
     </row>
